--- a/output/第10期計画_3町の社会資源一覧との突合.xlsx
+++ b/output/第10期計画_3町の社会資源一覧との突合.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_サービス別の従業員数" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_指定事業所一覧との網羅性" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_反映する箇所" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_計画素案とガイドの整合" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -170,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,6 +221,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5488,4 +5495,994 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>計画素案とサービスガイド構成案の事業所の記載の整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事業所数の出所は4つあり、時点と定義が異なる。サービス種別ごとに4出所を並べ、サービスガイド構成案の掲載件数と照合する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【1　サービス種別ごとの4出所の対照】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>① 見える化
+令和6年度</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>② 北海道一覧
+R8.6.30</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>③ 公表システム
+R8.8</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>④ 社会資源一覧
+基準日不明</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>ガイド
+掲載件数</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>所見</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも7。ただし公表システムは6で、北海道一覧の「訪問看護ステーション れもねーど」（東川町）を含まない。社会資源一覧は「だいだいの丘クリニック」（東神楽町）を含み、北海道一覧の訪問看護区分には現れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>訪問リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>北海道一覧は2。医療機関のみなし指定が現れないためとみられる。見える化・公表システム・社会資源一覧は3で一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>訪問入浴介護</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>区域内にゼロ（平成24年度から令和6年度まで）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>見える化は10。医科・歯科・薬局のみなし指定であり、北海道一覧・社会資源一覧には現れない。ガイドは富良野市と同じく「各病院・歯科医・薬剤師」の形とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>見える化10・公表システム10に対し、北海道一覧13・社会資源一覧11。北海道一覧にのみある3件は、回生苑居宅介護支援事業所（東神楽町）、ほの香居宅介護支援事業所（美瑛町）、ライフデザイン陽風（美瑛町）。うち回生苑は社会資源一覧の「回生会 居宅介護支援事業所」と同一とみられ、実質の差は2件</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>平成27年度に区域内の事業所がなくなった。ただし令和6・7年度とも延べ12人の給付実績があり区域外を利用している</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>短期入所療養介護</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも3で一致。社会資源一覧の東神楽町アゼリアハイツの2行のうち「地域老人福祉施設」は地域密着型として数える</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも3で一致。同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>見える化5・公表システム6・社会資源一覧6に対し北海道一覧7。差は「グループホーム くるみの郷」（東川町）で、北海道一覧に掲載があり見える化・公表システムにない（住まいと施設の公表名簿との突合で確認済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>4出所とも一致する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>区域内にゼロ。給付月額は平成30年度比＋36.4％で供給はすべて区域外の事業所による</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>制度創設以来13年間ゼロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>制度創設以来13年間ゼロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>制度創設以来13年間ゼロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>「―」はその出所に区分がないことを表す。④は社会資源一覧（サービス×事業所の行数）であり、ガイド構成案の掲載件数はこれと同じである。①〜③のうち値のあるものがすべて一致し、かつガイドの掲載件数と一致するものを緑とした（17件）。一致しないものは5件である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>【2　整合確認の結果】</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>確認した事項</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第3節1（区域内に事業所がないサービス11種別）とガイドの記載</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>整合している。ガイドは定期巡回・夜間対応・看多機の3種別を「区域内に事業所がないサービス」として掲げ、訪問入浴介護・認知症対応型通所介護・福祉用具貸与については編集メモで区域内ゼロである旨を注記した。</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日にガイドの編集メモを修正済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="76" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第3節2（見える化による事業所数の推移）とガイドの掲載件数</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援（見える化10・ガイド11）と認知症対応型共同生活介護（見える化5・ガイド6）の2件が一致しない。いずれも見える化が令和6年度、ガイドの基礎である社会資源一覧が令和8年8月20日受領であり、時点が異なることによる。</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>ガイドに時点を明記する。計画素案には注記を加える</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="76" customHeight="1">
+      <c r="A33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第3節6（北海道の名簿による施設・住まい）とガイドの掲載件数</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護が名簿7・ガイド6で一致しない。差は「グループホーム くるみの郷」（東川町）である。計画素案は同施設の定員を［要確認］としている。</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>ガイドに掲載するかどうかのご確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="76" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第3節7（北海道の介護保険事業所一覧）とガイドの掲載件数</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援が北海道13・ガイド11、訪問リハビリテーションが北海道2・ガイド3で一致しない。訪問介護13・訪問看護7・通所介護2・地域密着型通所介護4・小規模多機能型居宅介護5・短期入所生活介護5は一致する。</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援2件の掲載についてご確認を要する</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="76" customHeight="1">
+      <c r="A35" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>ガイドの名寄せの誤り</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>社会資源一覧の「地域老人福祉施設」（東神楽町アゼリアハイツ）を介護老人福祉施設に寄せていたため、介護老人福祉施設4・地域密着型介護老人福祉施設2となっていた。地域密着型に寄せることで3・3となり、見える化・北海道一覧・公表システムのいずれとも一致する。</t>
+        </is>
+      </c>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="17" t="n"/>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に修正済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="76" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>事業所の所在地</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>北海道「介護保険事業所一覧」「特別養護老人ホーム名簿」及び介護サービス情報公表システムにより、74事業所のうち73事業所の所在地を記載できた。記載できないのは「だいだいの丘クリニック」（東神楽町・訪問看護）1件である。</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>所在地は公表情報のため収録した。電話番号は記入枠のままとする</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>注1）事業所数は出所により異なる。見える化は年度の値、北海道の一覧は令和8年6月30日現在、公表システムは令和8年8月時点、社会資源一覧は基準日の記載がない。どれかが誤っているのではなく、時点と定義の違いである。
+注2）計画素案の中でも、第2章第3節2（見える化・令和6年度）と第3節7（北海道・令和8年6月30日現在）とで居宅介護支援の事業所数が10と13になっている。出所と時点を注記する必要がある。
+注3）ガイドを住民に配布する場合は、編集の時点で最新の公表資料により全件を洗い直す必要がある。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C31:G31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>